--- a/04_DESIGN_TABLES/DesignTable_2505.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2505.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,50 +451,55 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>PORTDEPTH@BORE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>THDMAJ_B@DRIVE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>THDMAJ_A@DRIVE</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>$PRP@TubeOD</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>$PRP@PartNo</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>$PRP@Threads</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>$PRP@DataStatus</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>$PRP@AxialSource</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>$COMMENT</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>$PRP@ScopeAction</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -521,43 +526,43 @@
       <c r="F3" t="n">
         <v>0.33</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.4375</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>0.405</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>1/4</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2505-04-02</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>7/16-20 (B UN/UNF-2A) x 1/8-27 (A NPTF)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Air-Way s149 only (double-pass 6 rows)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -584,43 +589,43 @@
       <c r="F4" t="n">
         <v>0.43</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>0.4375</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.54</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>1/4</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2505-04-04</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>7/16-20 (B UN/UNF-2A) x 1/4-18 (A NPTF)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Air-Way s149 only (double-pass 6 rows)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -647,43 +652,43 @@
       <c r="F5" t="n">
         <v>0.57</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.5625</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.675</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>3/8</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2505-06-06</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>9/16-18 (B UN/UNF-2A) x 3/8-18 (A NPTF)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Air-Way s149 only (double-pass 6 rows)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -710,43 +715,43 @@
       <c r="F6" t="n">
         <v>0.7</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.75</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0.84</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2505-08-08</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>3/4-16 (B UN/UNF-2A) x 1/2-14 (A NPTF)</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Air-Way s149 only (double-pass 6 rows)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 2505-08-08-FG</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -773,43 +778,43 @@
       <c r="F7" t="n">
         <v>0.91</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1.0625</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>1.05</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>2505-12-12</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1 1/16-12 (B UN/UNF-2A) x 3/4-14 (A NPTF)</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Air-Way s149 only (double-pass 6 rows)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 2505-12-12-FG</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -836,43 +841,43 @@
       <c r="F8" t="n">
         <v>1.14</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1.3125</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>1.315</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2505-16-16</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1 5/16-12 (B UN/UNF-2A) x 1-11 1/2 (A NPTF)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Air-Way s149 only (double-pass 6 rows)</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 2505-16-16-FG</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -884,32 +889,53 @@
           <t>2505-08-08-FG</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="B9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>2505-08-08-FG</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2505-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2505-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2505-08-08 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (staged): M2@DRIVE: OMi Items row 793 M 1 Size = 1.040; N6@DRIVE: OMi Items row 793 M 2 Size = 0.940; Y1@HEX: OMi Items row 793 Hex Flat = 1.062; D@BORE: OMi Items row 793 Side 1 ID = 0.391; THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (end library); THDMAJ_A@DRIVE: 1/2-14 -&gt; 0.84 (end library); TAPDRILL@BORE: end-library tap drill of the -08 pipe port = 0.7 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2505-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): body from OMi Items row 793, ports from the end library (not from its own Brennan file) - ASSUMED (one source)</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>2505-08-08-FG</t>
         </is>
@@ -921,32 +947,53 @@
           <t>2505-12-12-FG</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="B10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>2505-12-12-FG</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2505-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2505-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / Hex Flat / Side 1 ID = JIC leg / female pipe leg / body hex / JIC bore (Brennan TFA catalog p27 drawing M / N / Y / B1; Brennan 2505-08-08-FG STEP: JIC tip 1.040, female face 0.940, A/F 1.062, bore 0.391 = OMi row 793)); OMi = Brennan data (Brennan catalog TFA p27 (MJ-FP 45 DEG ELBOW) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts; female port tap drill / thread length: NO source yet (Q-TRANSFER-TAPDRILL) | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2505-12-12 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (staged): TAPDRILL@BORE: end-library tap drill of the -12 pipe port = 0.91 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>2026-10-02 (JIC-TEES): stays MISSING ONLY for the female port (TAPDRILL@BORE, PORTDEPTH@BORE): OMi / the catalog print no tap drill and no Brennan STEP of this part is in the repo - every other cell is now filled from OMi (Q-TRANSFER-TAPDRILL; candidates in proposals/) | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2505-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): the female port now takes the end-library tap drill and MS51503 P1 - ASSUMED (one source)</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>2505-12-12-FG</t>
         </is>
@@ -958,32 +1005,53 @@
           <t>2505-16-16-FG</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="B11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>2505-16-16-FG</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2505-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2505-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / Hex Flat / Side 1 ID = JIC leg / female pipe leg / body hex / JIC bore (Brennan TFA catalog p27 drawing M / N / Y / B1; Brennan 2505-08-08-FG STEP: JIC tip 1.040, female face 0.940, A/F 1.062, bore 0.391 = OMi row 793)); OMi = Brennan data (Brennan catalog TFA p27 (MJ-FP 45 DEG ELBOW) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts; female port tap drill / thread length: NO source yet (Q-TRANSFER-TAPDRILL) | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2505-16-16 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (staged): TAPDRILL@BORE: end-library tap drill of the -16 pipe port = 1.14 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>2026-10-02 (JIC-TEES): stays MISSING ONLY for the female port (TAPDRILL@BORE, PORTDEPTH@BORE): OMi / the catalog print no tap drill and no Brennan STEP of this part is in the repo - every other cell is now filled from OMi (Q-TRANSFER-TAPDRILL; candidates in proposals/) | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2505-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): the female port now takes the end-library tap drill and MS51503 P1 - ASSUMED (one source)</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>2505-16-16-FG</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_2505.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2505.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1054,6 +1059,132 @@
       <c r="Q11" t="inlineStr">
         <is>
           <t>2505-16-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2505-04-04-FG</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2505-04-04-FG</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; legs / flats / bore: OMi WebsitePartsInfo2026 Items (= Brennan TFA p.27, one source); tap drill = Air-Way per size (A1); JIC end MS33656J</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; legs / flats / bore from OMi Items (= Brennan TFA p.27, one source); end details from the end library</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2505-04-04-FG</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>OMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2505-06-06-FG</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2505-06-06-FG</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; legs / flats / bore: OMi WebsitePartsInfo2026 Items (= Brennan TFA p.27, one source); tap drill = Air-Way per size (A1); JIC end MS33656J</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; legs / flats / bore from OMi Items (= Brennan TFA p.27, one source); end details from the end library</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2505-06-06-FG</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_2505.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2505.xlsx
@@ -909,6 +909,9 @@
       <c r="F9" t="n">
         <v>0.7</v>
       </c>
+      <c r="G9" t="n">
+        <v>0.75</v>
+      </c>
       <c r="H9" t="n">
         <v>0.75</v>
       </c>
@@ -927,12 +930,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2505-08-08 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (staged): M2@DRIVE: OMi Items row 793 M 1 Size = 1.040; N6@DRIVE: OMi Items row 793 M 2 Size = 0.940; Y1@HEX: OMi Items row 793 Hex Flat = 1.062; D@BORE: OMi Items row 793 Side 1 ID = 0.391; THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (end library); THDMAJ_A@DRIVE: 1/2-14 -&gt; 0.84 (end library); TAPDRILL@BORE: end-library tap drill of the -08 pipe port = 0.7 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED</t>
+          <t>[BRENNAN-CELL 2026-10-21: PORTDEPTH@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2505-08-08 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (staged): M2@DRIVE: OMi Items row 793 M 1 Size = 1.040; N6@DRIVE: OMi Items row 793 M 2 Size = 0.940; Y1@HEX: OMi Items row 793 Hex Flat = 1.062; D@BORE: OMi Items row 793 Side 1 ID = 0.391; THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (end library); THDMAJ_A@DRIVE: 1/2-14 -&gt; 0.84 (end library); TAPDRILL@BORE: end-library tap drill of the -08 pipe port = 0.7 (the value every built female pipe port of that size carries, = Air-Way's per-size value; user 2026-10-08 Q-TRANSFER-ENDLIB "reuse end details - yes"); female port thread length = MS51503 P1 (library, no PORTDEPTH from a Brennan file) [user 2026-09-25 OMi dims; 2026-10-08 end library = yes; Brennan for shape only] -&gt; ASSUMED | PORTDEPTH@BORE: Brennan port depth -08 = 0.750 measured on this part's own STEP 09_STEP_FILES/BRENNAN_2505-08-08-FG.stp (forged.py NPTFF leg at 45 deg: taper depth from the face 0.75, mouth 0.0315; brennan_port_depths.run 0.7500; C_ownstep/measure/2505-08-08-FG.txt) = the -08 value of gen_tee ANGLED_P1_NOTE (Q-ANGLED-P1, settled from the Brennan STEPs 2026-10-18: the MS51503 P1 0.90 does not fit the 0.94 leg of the 45 deg elbow)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2505-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): body from OMi Items row 793, ports from the end library (not from its own Brennan file) - ASSUMED (one source)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2505-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): body from OMi Items row 793, ports from the end library (not from its own Brennan file) - ASSUMED (one source) | 2026-10-21 batch 19 C (staged): PORTDEPTH@BORE 0.75 from the own Brennan STEP (Q-ANGLED-P1); the body stays OMi Items row 793</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -943,6 +946,11 @@
       <c r="Q9" t="inlineStr">
         <is>
           <t>2505-08-08-FG</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
